--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20460,7 +20478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20509,6 +20527,57 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0023</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1971_72_0023 'Kvalifikace o ČNHL' (L25, parent=NODE_S1971_72_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0027</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1971_72_0027 'KVAL skupina A' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0028</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1971_72_0028 'KVAL skupina B' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -58598,6 +58667,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0023</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1971_72_0023 'Kvalifikace o ČNHL' (L25, parent=NODE_S1971_72_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0027</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1971_72_0027 'KVAL skupina A' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0028</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1971_72_0028 'KVAL skupina B' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20478,7 +20478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20531,14 +20531,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S1971_72_0023</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1971_72_0023 'Kvalifikace o ČNHL' (L25, parent=NODE_S1971_72_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -20548,14 +20543,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1971_72_0027</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1971_72_0027 'KVAL skupina A' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20565,17 +20555,492 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1971_72_0028</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1971_72_0028 'KVAL skupina B' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1970_71_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: která Kamenice — pravděpodobně u Jílového?). K ověření.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Benešov' → 'Zruč nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0492 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0382 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27703,7 +28168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J567"/>
+  <dimension ref="A1:J574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -28004,12 +28469,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28434,12 +28899,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28560,12 +29025,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -28948,12 +29413,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -28990,12 +29455,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -29751,12 +30216,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -30186,12 +30651,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -30312,12 +30777,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -30616,12 +31081,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -30915,12 +31380,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Litoměřice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -31046,12 +31511,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32944,12 +33409,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha.</t>
+          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha. || TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>VS Technika</t>
         </is>
       </c>
     </row>
@@ -32986,12 +33451,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Ruzyne = TJ Ruzyně EGU (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 6 (letiste). **EGU** = Energeticky vyzkumny ustav nebo Elektrotechnicky/Energo podnik. city Praha (Ruzyně).</t>
+          <t>Ruzyne = TJ Ruzyně EGU (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 6 (letiste). **EGU** = Energeticky vyzkumny ustav nebo Elektrotechnicky/Energo podnik. city Praha (Ruzyně). || TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Praha (Ruzyně)</t>
+          <t>Ruzyně EGU</t>
         </is>
       </c>
     </row>
@@ -35549,12 +36014,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -36110,12 +36575,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
+          <t>Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov. || TBD: city 'Benešov' → 'Zruč nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Benešov</t>
+          <t>Zruč nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -37361,12 +37826,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38298,12 +38763,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -38971,12 +39436,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -39980,12 +40445,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -43398,12 +43863,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -43670,12 +44135,12 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -46339,12 +46804,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány.</t>
+          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány. || TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Lány</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -46381,12 +46846,12 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány.</t>
+          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány. || TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Lány</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -46690,12 +47155,12 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -46779,12 +47244,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (vyrobce kovacich/lisovacich strojů). Patterns: Tatran -&gt; Spartak -&gt; ŽĎAS Žďár nL Sázavou. city Žďár nad Sázavou.</t>
+          <t>Žďár nad Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (vyrobce kovacich/lisovacich strojů). Patterns: Tatran -&gt; Spartak -&gt; ŽĎAS Žďár nL Sázavou. city Žďár nad Sázavou. || TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -47481,12 +47946,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Nářadí Zborovice</t>
         </is>
       </c>
     </row>
@@ -48939,12 +49404,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -50286,12 +50751,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -52615,6 +53080,230 @@
       <c r="J567" t="inlineStr">
         <is>
           <t>Semechnice</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0225</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0282</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0299</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0338</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>30SVRC</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0434</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0511</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>30JHMR</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0560</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>L100</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58673,11 +59362,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -58722,21 +59411,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1971_72_0023</t>
+          <t>CLUB_S1971_72_0006</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1971_72_0023 'Kvalifikace o ČNHL' (L25, parent=NODE_S1971_72_0014) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -58744,21 +59431,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1971_72_0027</t>
+          <t>CLUB_S1971_72_0016</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1971_72_0027 'KVAL skupina A' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -58766,24 +59451,822 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1971_72_0028</t>
+          <t>CLUB_S1971_72_0019</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1971_72_0028 'KVAL skupina B' (L35, parent=NODE_S1971_72_0026) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0028</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0029</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0036</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0047</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0057</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0060</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0067</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0074</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0077</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0120</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1970_71_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0127</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0128</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0148</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: která Kamenice — pravděpodobně u Jílového?). K ověření.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0187</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0201</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Benešov' → 'Zruč nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0230</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0251</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0259</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0265</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0288</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0369</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0375</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0425</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0432</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0433</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0441</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0443</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0459</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0476</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0487</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0492 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0493</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0525</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0580</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0382 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0225</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0282</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0299</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0338</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0434</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0511</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1971_72_0560</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -73514,6 +74997,11 @@
           <t>CLUB_S1970_71_0164</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V89" t="inlineStr">
         <is>
           <t>TR_S1971_72_00244</t>
@@ -73591,6 +75079,11 @@
       <c r="R91" t="inlineStr">
         <is>
           <t>CLUB_S1970_71_0156</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">

--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20478,7 +20478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20533,7 +20533,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -20545,7 +20545,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20557,7 +20557,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20569,7 +20569,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20581,7 +20581,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20593,7 +20593,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1970_71_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20605,7 +20605,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20617,7 +20617,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: která Kamenice — pravděpodobně u Jílového?). K ověření.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20629,7 +20629,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20641,7 +20641,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20653,7 +20653,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20665,7 +20665,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20677,7 +20677,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1970_71_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20689,7 +20689,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20701,7 +20701,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20713,7 +20713,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: která Kamenice — pravděpodobně u Jílového?). K ověření.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20725,7 +20725,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20737,7 +20737,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Benešov' → 'Zruč nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20749,7 +20749,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0492 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20761,7 +20761,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0382 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20773,7 +20773,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -20785,7 +20785,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20797,7 +20797,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20809,7 +20809,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20821,7 +20821,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20833,7 +20833,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20845,202 +20845,10 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0492 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0382 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -21057,7 +20865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21116,6 +20924,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21158,6 +20971,11 @@
           <t>10 týmů, jeden stůl. Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21205,6 +21023,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21373,6 +21196,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21415,6 +21243,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21457,6 +21290,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21504,6 +21342,11 @@
           <t>Základní část SNHL, na ni navazují skupina A a skupina B.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21630,6 +21473,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21672,6 +21520,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0011</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21714,6 +21567,11 @@
           <t>Divize: 6 skupin CZ (A-F) + 2 skupiny SVK + kvalifikace o I.ČNHL.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0012</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21756,6 +21614,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0013</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21798,6 +21661,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0014</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21840,6 +21708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0015</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21882,6 +21755,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0016</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21924,6 +21802,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0017</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21966,6 +21849,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0018</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -22097,6 +21985,11 @@
           <t>Vítězové skupin Divize. Postupuje se do I.ČNHL.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0019</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22139,6 +22032,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0020</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -22181,6 +22079,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0021</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -22228,6 +22131,11 @@
           <t>Prepared/raw používá starý titul "Kvalifikace o postup do II.ligy"; PDF pro ročník 1971/72 uvádí "Kvalifikace o divizi". Výstup metodicky veden podle PDF.</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0022</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22270,6 +22178,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0023</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -22312,6 +22225,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0024</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -22354,6 +22272,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -22522,6 +22445,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0030</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -22564,6 +22492,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0031</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -22690,6 +22623,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0034</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -22816,6 +22754,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22942,6 +22885,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22984,6 +22932,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0042</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -23026,6 +22979,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0043</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -23068,6 +23026,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0044</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -23162,6 +23125,11 @@
           <t>Kvalifikace o I.B třídu</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0045</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -23204,6 +23172,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0046</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -23246,6 +23219,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0047</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -23330,6 +23308,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0049</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -23372,6 +23355,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0050</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -23587,6 +23575,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0053</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -23629,6 +23622,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0054</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -23671,6 +23669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0055</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -23713,6 +23716,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0056</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -23755,6 +23763,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0057</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -23797,6 +23810,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0058</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -23839,6 +23857,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0059</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -23881,6 +23904,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0060</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -23923,6 +23951,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0061</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -23965,6 +23998,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0063</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -24012,6 +24050,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0064</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -24054,6 +24097,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0065</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -24096,6 +24144,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0066</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -24180,6 +24233,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0068</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -24222,6 +24280,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0069</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24264,6 +24327,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0070</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -24306,6 +24374,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0071</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -24353,6 +24426,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0072</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -24395,6 +24473,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0073</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24437,6 +24520,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0074</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24479,6 +24567,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0075</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24521,6 +24614,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0076</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -24563,6 +24661,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0077</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -24605,6 +24708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0078</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -24647,6 +24755,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0079</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -24689,6 +24802,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0080</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -24731,6 +24849,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0081</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -24773,6 +24896,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0082</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -24815,6 +24943,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0083</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -24909,6 +25042,11 @@
           <t>Kvalifikace</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0085</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -24951,6 +25089,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0086</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -24993,6 +25136,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0087</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25035,6 +25183,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0088</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -25077,6 +25230,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0089</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -25413,6 +25571,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0097</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -26048,6 +26211,11 @@
           <t>Kontejner slovenských krajských přeborů; paralelní větve stejné úrovně.</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0105</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -26090,6 +26258,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0106</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -26132,6 +26305,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0107</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -26172,6 +26350,11 @@
       <c r="J120" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>NODE_S1970_71_0108</t>
         </is>
       </c>
     </row>
@@ -28469,12 +28652,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28899,12 +29082,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -29025,12 +29208,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -29413,12 +29596,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29455,12 +29638,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -30216,12 +30399,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -31380,12 +31563,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Litoměřice</t>
         </is>
       </c>
     </row>
@@ -33409,12 +33592,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha. || TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>VS Technika</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -36575,12 +36758,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov. || TBD: city 'Benešov' → 'Zruč nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Horní Benešov = Spartak Horní Benešov (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Bruntal). POZOR: Dolni Benesov u Opavy! Vsichni Benešovi v okrese - Horni, Dolni, Benesov u Prahy. city Horní Benešov.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Zruč nad Sázavou</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -43863,12 +44046,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -44135,12 +44318,12 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -46804,12 +46987,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány. || TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány.</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Lány</t>
         </is>
       </c>
     </row>
@@ -46846,12 +47029,12 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány. || TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava překlepu „Lany" → „Lány". city: Lany → „Lány". Smart fix prev: chybělo → 51/52 0039 (Sokol Lány). Identity transition Sokol → Tatran (D28). V Lánech jediný klub — kontinuita jasná (potvrzeno Pavlem). || Lány = Sokol/Tatran Lány (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). city Lány.</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Lány</t>
         </is>
       </c>
     </row>
@@ -47946,12 +48129,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha. || TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Praha Sokolovo = HC Sparta Praha (Wiki D42 - registr ustavy 04/2026). Chain AC Sparta -&gt; Spartak Praha Sokolovo (1953-1965) -&gt; Sparta Praha. city Praha.</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Nářadí Zborovice</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -49404,12 +49587,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -50751,12 +50934,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -59362,7 +59545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -59416,12 +59599,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0006</t>
+          <t>CLUB_S1971_72_0036</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -59436,12 +59619,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0016</t>
+          <t>CLUB_S1971_72_0057</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59456,12 +59639,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0019</t>
+          <t>CLUB_S1971_72_0060</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59476,12 +59659,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0028</t>
+          <t>CLUB_S1971_72_0067</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59496,12 +59679,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0029</t>
+          <t>CLUB_S1971_72_0077</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59516,12 +59699,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0036</t>
+          <t>CLUB_S1971_72_0120</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1970_71_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -59536,12 +59719,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0047</t>
+          <t>CLUB_S1971_72_0128</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59556,12 +59739,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0057</t>
+          <t>CLUB_S1971_72_0148</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: která Kamenice — pravděpodobně u Jílového?). K ověření.</t>
         </is>
       </c>
     </row>
@@ -59576,12 +59759,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0060</t>
+          <t>CLUB_S1971_72_0187</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59596,12 +59779,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0067</t>
+          <t>CLUB_S1971_72_0230</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59616,12 +59799,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0074</t>
+          <t>CLUB_S1971_72_0251</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59636,12 +59819,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0077</t>
+          <t>CLUB_S1971_72_0259</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -59656,12 +59839,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0120</t>
+          <t>CLUB_S1971_72_0265</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1970_71_0122 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59676,12 +59859,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0127</t>
+          <t>CLUB_S1971_72_0288</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59696,12 +59879,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0128</t>
+          <t>CLUB_S1971_72_0425</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha (Ruzyně)' → 'Ruzyně EGU' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -59716,12 +59899,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0148</t>
+          <t>CLUB_S1971_72_0441</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: která Kamenice — pravděpodobně u Jílového?). K ověření.</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59736,12 +59919,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0187</t>
+          <t>CLUB_S1971_72_0443</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59756,12 +59939,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0201</t>
+          <t>CLUB_S1971_72_0476</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Benešov' → 'Zruč nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -59776,12 +59959,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0230</t>
+          <t>CLUB_S1971_72_0487</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0492 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -59796,12 +59979,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0251</t>
+          <t>CLUB_S1971_72_0580</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0382 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -59816,12 +59999,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0259</t>
+          <t>CLUB_S1971_72_0225</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59836,12 +60019,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0265</t>
+          <t>CLUB_S1971_72_0282</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59856,12 +60039,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0288</t>
+          <t>CLUB_S1971_72_0299</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59876,12 +60059,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0369</t>
+          <t>CLUB_S1971_72_0338</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59896,12 +60079,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0375</t>
+          <t>CLUB_S1971_72_0434</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59916,12 +60099,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0425</t>
+          <t>CLUB_S1971_72_0511</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59936,337 +60119,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1971_72_0432</t>
+          <t>CLUB_S1971_72_0560</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0433</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Lány' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0441</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0443</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0459</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Praha' → 'Nářadí Zborovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0476</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0487</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0492 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0493</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0525</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0580</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1970_71_0382 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0225</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
           <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0282</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0299</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0338</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0434</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0511</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1971_72_0560</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: doplněno z standings (orphan) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -53983,7 +53983,7 @@
         <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -57509,7 +57509,7 @@
         <v>7</v>
       </c>
       <c r="J54" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M55" t="n">
         <v>27</v>
@@ -57743,7 +57743,7 @@
         <v>9</v>
       </c>
       <c r="J57" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M57" t="n">
         <v>24</v>
@@ -57899,7 +57899,7 @@
         <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M61" t="n">
         <v>18</v>
@@ -58146,7 +58146,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M62" t="n">
         <v>10</v>
@@ -58570,7 +58570,7 @@
         <v>11</v>
       </c>
       <c r="J68" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -59005,7 +59005,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M74" t="n">
         <v>31</v>

--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -20865,7 +20865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:N123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20927,6 +20927,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -21196,6 +21196,16 @@
           <t>NODE_S1971_72_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21210,6 +21220,14 @@
         <is>
           <t>NODE_S1970_71_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -21243,6 +21261,8 @@
           <t>NODE_S1971_72_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21257,6 +21277,14 @@
         <is>
           <t>NODE_S1970_71_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -21290,6 +21318,8 @@
           <t>NODE_S1971_72_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21304,6 +21334,14 @@
         <is>
           <t>NODE_S1970_71_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21337,6 +21375,8 @@
           <t>NODE_S1971_72_0003</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21356,6 +21396,14 @@
         <is>
           <t>NODE_S1970_71_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -21389,6 +21437,8 @@
           <t>NODE_S1971_72_0003</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21398,6 +21448,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -21896,6 +21954,8 @@
           <t>NODE_S1971_72_0020</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21905,6 +21965,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -21938,6 +22006,8 @@
           <t>NODE_S1971_72_0020</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21947,6 +22017,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -22623,6 +22701,8 @@
           <t>NODE_S1971_72_0033</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22637,6 +22717,14 @@
         <is>
           <t>NODE_S1970_71_0034</t>
         </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -23167,6 +23255,12 @@
           <t>REG_JHC</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0054</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23186,6 +23280,14 @@
         <is>
           <t>NODE_S1970_71_0046</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -23402,6 +23504,8 @@
           <t>NODE_S1971_72_0049</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23411,6 +23515,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -23763,6 +23875,8 @@
           <t>NODE_S1971_72_0058</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23777,6 +23891,14 @@
         <is>
           <t>NODE_S1970_71_0057</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -24092,6 +24214,12 @@
           <t>REG_SEC</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0077</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24111,6 +24239,14 @@
         <is>
           <t>NODE_S1970_71_0065</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -24473,6 +24609,12 @@
           <t>NODE_S1971_72_0069</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0078</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24487,6 +24629,14 @@
         <is>
           <t>NODE_S1970_71_0073</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -24520,6 +24670,8 @@
           <t>NODE_S1971_72_0069</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24534,6 +24686,14 @@
         <is>
           <t>NODE_S1970_71_0074</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -24755,6 +24915,8 @@
           <t>NODE_S1971_72_0079</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24769,6 +24931,14 @@
         <is>
           <t>NODE_S1970_71_0079</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -25786,6 +25956,8 @@
           <t>NODE_S1971_72_0101</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25795,6 +25967,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -25870,6 +26050,8 @@
           <t>NODE_S1971_72_0101</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25879,6 +26061,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -25954,6 +26144,8 @@
           <t>NODE_S1971_72_0101</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25963,6 +26155,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -26399,6 +26599,16 @@
           <t>NODE_S1971_72_0016</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0021</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0022</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26413,6 +26623,14 @@
         <is>
           <t>Základní skupina. Ve výstupním listu je strukturálně oddělena; řádky finálových částí jsou vedeny samostatně.</t>
         </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -26488,6 +26706,8 @@
           <t>NODE_S1971_72_0016</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26497,6 +26717,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/S1971_72_FINAL.xlsx
+++ b/data/S1971_72_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -21261,8 +21266,6 @@
           <t>NODE_S1971_72_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21318,8 +21321,6 @@
           <t>NODE_S1971_72_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21375,8 +21376,6 @@
           <t>NODE_S1971_72_0003</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21437,8 +21436,6 @@
           <t>NODE_S1971_72_0003</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21954,8 +21951,6 @@
           <t>NODE_S1971_72_0020</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22006,8 +22001,6 @@
           <t>NODE_S1971_72_0020</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22701,8 +22694,6 @@
           <t>NODE_S1971_72_0033</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23260,7 +23251,6 @@
           <t>NODE_S1971_72_0054</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23504,8 +23494,6 @@
           <t>NODE_S1971_72_0049</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23875,8 +23863,6 @@
           <t>NODE_S1971_72_0058</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24219,7 +24205,6 @@
           <t>NODE_S1971_72_0077</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24614,7 +24599,6 @@
           <t>NODE_S1971_72_0078</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24670,8 +24654,6 @@
           <t>NODE_S1971_72_0069</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24915,8 +24897,6 @@
           <t>NODE_S1971_72_0079</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25956,8 +25936,6 @@
           <t>NODE_S1971_72_0101</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26050,8 +26028,6 @@
           <t>NODE_S1971_72_0101</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26144,8 +26120,6 @@
           <t>NODE_S1971_72_0101</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26706,8 +26680,6 @@
           <t>NODE_S1971_72_0016</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -59529,7 +59501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59769,6 +59741,18 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>TJ Sokol Sloup (JM) a VTJ Dukla Valašské Meziříčí (SM) postoupily do divize přímo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>
